--- a/artfynd/A 35247-2022 artfynd.xlsx
+++ b/artfynd/A 35247-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35247-2022 artfynd.xlsx
+++ b/artfynd/A 35247-2022 artfynd.xlsx
@@ -1118,11 +1118,11 @@
         <v>113155097</v>
       </c>
       <c r="B6" t="n">
-        <v>90774</v>
+        <v>91168</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2028,11 +2028,11 @@
         <v>113155243</v>
       </c>
       <c r="B14" t="n">
-        <v>90774</v>
+        <v>91168</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">

--- a/artfynd/A 35247-2022 artfynd.xlsx
+++ b/artfynd/A 35247-2022 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>113155097</v>
       </c>
       <c r="B6" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>113155243</v>
       </c>
       <c r="B14" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 35247-2022 artfynd.xlsx
+++ b/artfynd/A 35247-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113155230</v>
+        <v>113155919</v>
       </c>
       <c r="B2" t="n">
-        <v>90346</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662750</v>
+        <v>662630</v>
       </c>
       <c r="R2" t="n">
-        <v>7278140</v>
+        <v>7278125</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,12 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113155182</v>
+        <v>113155190</v>
       </c>
       <c r="B3" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662780</v>
+        <v>662770</v>
       </c>
       <c r="R3" t="n">
-        <v>7278220</v>
+        <v>7278205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,37 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113155980</v>
+        <v>113155210</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662595</v>
+        <v>662695</v>
       </c>
       <c r="R4" t="n">
-        <v>7278205</v>
+        <v>7278155</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,37 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113155221</v>
+        <v>113155230</v>
       </c>
       <c r="B5" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662690</v>
+        <v>662750</v>
       </c>
       <c r="R5" t="n">
-        <v>7278150</v>
+        <v>7278140</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113155097</v>
+        <v>113155951</v>
       </c>
       <c r="B6" t="n">
-        <v>91194</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,14 +1133,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sotträskberget, Pi lm</t>
+          <t>Fiskträskberget, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>663240</v>
+        <v>662575</v>
       </c>
       <c r="R6" t="n">
-        <v>7278520</v>
+        <v>7278170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,12 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,37 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113155193</v>
+        <v>113155967</v>
       </c>
       <c r="B7" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662770</v>
+        <v>662600</v>
       </c>
       <c r="R7" t="n">
-        <v>7278205</v>
+        <v>7278180</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,12 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,15 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113155210</v>
+        <v>113155097</v>
       </c>
       <c r="B8" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1378,14 +1343,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fiskträskberget, Pi lm</t>
+          <t>Sotträskberget, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662695</v>
+        <v>663240</v>
       </c>
       <c r="R8" t="n">
-        <v>7278155</v>
+        <v>7278520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,15 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113155253</v>
+        <v>113155243</v>
       </c>
       <c r="B9" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1461,21 +1421,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662880</v>
+        <v>662870</v>
       </c>
       <c r="R9" t="n">
-        <v>7278110</v>
+        <v>7278150</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,15 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113155967</v>
+        <v>113155221</v>
       </c>
       <c r="B10" t="n">
-        <v>90346</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662600</v>
+        <v>662690</v>
       </c>
       <c r="R10" t="n">
-        <v>7278180</v>
+        <v>7278150</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,12 +1587,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,12 +1623,7 @@
         <v>113155198</v>
       </c>
       <c r="B11" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,57 +1725,52 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113155060</v>
+        <v>113155980</v>
       </c>
       <c r="B12" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sotträskberget, Pi lm</t>
+          <t>Fiskträskberget, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>663285</v>
+        <v>662595</v>
       </c>
       <c r="R12" t="n">
-        <v>7278500</v>
+        <v>7278205</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,12 +1797,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1869,36 +1814,6 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>flerskiktad gammal granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>vanlig rönn</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia subsp. aucuparia</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>jättegrov gammal rönn</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia subsp. aucuparia # jättegrov gammal rönn</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1918,16 +1833,11 @@
         <v>113155072</v>
       </c>
       <c r="B13" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2025,15 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113155243</v>
+        <v>113155413</v>
       </c>
       <c r="B14" t="n">
-        <v>91194</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2041,41 +1946,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fiskträskberget, Pi lm</t>
+          <t>Sotträskberget, Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662870</v>
+        <v>663215</v>
       </c>
       <c r="R14" t="n">
-        <v>7278150</v>
+        <v>7278535</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,15 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113155119</v>
+        <v>113155060</v>
       </c>
       <c r="B15" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>663240</v>
+        <v>663285</v>
       </c>
       <c r="R15" t="n">
-        <v>7278520</v>
+        <v>7278500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,27 +2137,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Gammal flerskiktad granskog</t>
+          <t>flerskiktad gammal granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vanlig rönn</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Sorbus aucuparia subsp. aucuparia</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>på en gammal björk</t>
+          <t>jättegrov gammal rönn</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Betula # på en gammal björk</t>
+          <t>Sorbus aucuparia subsp. aucuparia # jättegrov gammal rönn</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2275,15 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113155951</v>
+        <v>113155119</v>
       </c>
       <c r="B16" t="n">
-        <v>90346</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,41 +2186,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fiskträskberget, Pi lm</t>
+          <t>Sotträskberget, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>662575</v>
+        <v>663240</v>
       </c>
       <c r="R16" t="n">
-        <v>7278170</v>
+        <v>7278520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,12 +2247,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,6 +2265,36 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Gammal flerskiktad granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>på en gammal björk</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Betula # på en gammal björk</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
@@ -2382,226 +2307,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>113155190</v>
-      </c>
-      <c r="B17" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>658</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Fiskträskberget, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>662770</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7278205</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>113155413</v>
-      </c>
-      <c r="B18" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Sotträskberget, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>663215</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7278535</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35247-2022 artfynd.xlsx
+++ b/artfynd/A 35247-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155919</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155190</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155210</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155230</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155951</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155967</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155097</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155243</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155221</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155198</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155980</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155072</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155413</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2172,6 +2242,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155060</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2307,8 +2382,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113155119</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>